--- a/Data/LookUp.xlsx
+++ b/Data/LookUp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\european-average-earnings-index\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A6D7BB-2164-4A72-9DC2-940E5A1F1B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7BE8EA-20C0-4B76-9CFC-D5D7EDD78AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="country" sheetId="2" r:id="rId1"/>
@@ -1067,7 +1067,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
